--- a/Documentation dashboards.xlsx
+++ b/Documentation dashboards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/D-DE-Dploiementdesdashboards/Documents partages/Déploiement des dashboards/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/02 - Données/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="8_{E38240D2-6D03-460C-AD1F-56A7CB9B1EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B9BC34A-31AC-4BB5-BD3B-2E9E562EEF3C}"/>
+  <xr:revisionPtr revIDLastSave="217" documentId="8_{E38240D2-6D03-460C-AD1F-56A7CB9B1EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{492BDCE6-1795-4836-BDB7-7DBFD40DC648}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{78D94C61-402A-46A6-8F9B-6154C169E404}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="1" activeTab="1" xr2:uid="{78D94C61-402A-46A6-8F9B-6154C169E404}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="150">
   <si>
     <t xml:space="preserve">Nombre de logements sociaux du parc  </t>
   </si>
@@ -316,21 +316,301 @@
 Calcul: Nombre de logements avec année (BAIL) = N-1 et année(LOCAT) &lt; N-1 / Nombre de logements avec année(LOCAT) &lt; N-1 et proposés à la location mais vacants OU loué avec contrat de location</t>
   </si>
   <si>
-    <t>Part de locataires sociaux</t>
-  </si>
-  <si>
-    <t>Pourcentage de logements sociaux occupés au sein du parc de résidences principales
-Calcul: Nombre de logements sociaux occupés (mode d'occupation = 1,4,5,6) / Nombre de résidences principales</t>
-  </si>
-  <si>
-    <t>Ordre</t>
+    <t>Taux de locataires sociaux</t>
+  </si>
+  <si>
+    <t>Calcul: Nombre de logements sociaux occupés / Nombre de résidences principales privées</t>
+  </si>
+  <si>
+    <t>Demande et attribution</t>
+  </si>
+  <si>
+    <t>Le rapport sur les demandes et les attributions de logements sociaux est réalisé à partir des données du Système National d’Enregistrement (SNE). Il met en parallèle le profil des demandeurs avec celui des attributaires de logements sociaux et montre l’adéquation entre les attributions et la demande au travers de différents indicateurs. 
+Sont considérés comme « demandeurs » les demandeurs en attente d’un logement social à fin décembre &lt;annee&gt; et sont comptés comme « attributaires » les ménages ayant emménagé dans un logement social durant l’année &lt;annee&gt;. Les chiffres et indicateurs présentés sur le tableau de bord ne prennent pas en compte la demande des associations, mais uniquement celle des demandeurs physiques</t>
+  </si>
+  <si>
+    <t>SNE, INSEE</t>
+  </si>
+  <si>
+    <t>Nombre de demandes/demandeurs</t>
+  </si>
+  <si>
+    <t>Nombre de nouvelles demandes</t>
+  </si>
+  <si>
+    <t>Nombre de demandes en mutation</t>
+  </si>
+  <si>
+    <t>Part des nouvelles demandes</t>
+  </si>
+  <si>
+    <t>Part des demandes en mutation</t>
+  </si>
+  <si>
+    <t>Ancienneté de la demande</t>
+  </si>
+  <si>
+    <t>Pression de la demande</t>
+  </si>
+  <si>
+    <t>Nombre de primo-demandeurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ressources / mois / UC </t>
+  </si>
+  <si>
+    <t>Nombre d'attributions/attributaires</t>
+  </si>
+  <si>
+    <t>Nombre d'attributions en mutation</t>
+  </si>
+  <si>
+    <t>Part des attributions en mutation</t>
+  </si>
+  <si>
+    <t>Délai d'attribution</t>
+  </si>
+  <si>
+    <t>Taux de succès</t>
+  </si>
+  <si>
+    <t>Nombre de personnes seules</t>
+  </si>
+  <si>
+    <t>Nombre  de jeunes ménages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taille de ménage  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age moyen  </t>
+  </si>
+  <si>
+    <t>Part des personnes seules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenus N-2  </t>
+  </si>
+  <si>
+    <t>Composition familiale</t>
+  </si>
+  <si>
+    <t>Tranche de ressources par UC</t>
+  </si>
+  <si>
+    <t>Mode de logement</t>
+  </si>
+  <si>
+    <t>Nombre de pièces adéquation</t>
+  </si>
+  <si>
+    <t>Motif de la demande</t>
+  </si>
+  <si>
+    <t>Tranche d'ancienneté demande / délai d'attribution</t>
+  </si>
+  <si>
+    <t>Localisation</t>
+  </si>
+  <si>
+    <t>Tranche de plafonds de ressources</t>
+  </si>
+  <si>
+    <t>Tranche d'âge</t>
+  </si>
+  <si>
+    <t>Motif de radiation</t>
+  </si>
+  <si>
+    <t>Nombre de ménages demandeurs en attente d'un logement social à fin décembre</t>
+  </si>
+  <si>
+    <t>Nombre de ménages demandeurs, actuellement locataires Hlm, en attente d'un logement social à fin décembre de l'année sélectionnée</t>
+  </si>
+  <si>
+    <t>Nombre d'attributions de logements sociaux réalisées durant l'année séléctionnée</t>
+  </si>
+  <si>
+    <t>Nombre d'attributions réalisées durant l'année sélectionnée pour des ménages changeant de logement au sein du parc Hlm</t>
+  </si>
+  <si>
+    <t>Rapport entre le nombre de logements attribués sur l'année sélectionnée et le nombre de demande en stock à fin de l'année sélectionnée</t>
+  </si>
+  <si>
+    <t>Répartition des demandeurs et des attributaires selon la composition familiale du ménage</t>
+  </si>
+  <si>
+    <t>verifier pour le co titulaire couple
+verifier famille mono</t>
+  </si>
+  <si>
+    <t>Isolé: Ménage formé d'une seule personne
+Famille monoparentale: Ménage où une seule personne est titulaire du bail ayant une ou plusieurs personne(s) à charge dont le lien avec le demandeur et la différence d'âge s'apparente à un lien de parenté.
+Couple sans enfant: Ménage formé de deux personnes co-titulaires du bail dont le lien est d'être conjoints, pacsés ou concubins, sans personne à charge
+Autre: Ménages n'entrant pas dans les catégories sus-citées.</t>
+  </si>
+  <si>
+    <t>La dénomination "jeune ménage" recouvre ces catégories de ménage: 
+- les jeunes isolés de moins de 28 ans avec ou sans enfant(s)
+- les jeunes couples avec ou sans enfant(s)
+Jeune couple = couple marié (ou concubins cosignataires du bail) dont la somme des âges est au plus égale à 55 ans.</t>
+  </si>
+  <si>
+    <t>Ressources par unité de consommation
+Calcul: Ressources mensuelles du foyer / Nombre d'unités de consommation
+Les ressources comprennent l'ensemble des revenus: revenus du travail, pension de retraite, chômage, prestations sociales…</t>
+  </si>
+  <si>
+    <t>Répartition des demandeurs et des attributaires selon leur mode de logement antérieur</t>
+  </si>
+  <si>
+    <t>Répartition des demandeurs selon le type de logement recherché et celle des attributaires selon la typologie du logement attribué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motifs évoqués par les demandeurs </t>
+  </si>
+  <si>
+    <t>Perte de logement : Situations de démolition, de logement repris ou mis en vente par le propriétaire ou en procédure d'expulsion.
+Sans logement ou précaire/insalubre: Sans logement, hébergé/logement temporaire ou situation de logement non décent, insalubre, dangereux ou impropre à l'habitation.
+Evénements familiaux: Situation de divorce, séparation, décohabitation, futur mariage, concubinage ou PACS, regroupement familial ou volonté de se rapprocher de la famille.
+Rapprochement travail/comodités: Situations de mutation professionnelle, de rapprochement du lieu de travail, rapprochement des équipements et services du fait d'un(e) assistant(e) maternelle ou familiale.
+Handicap/Santé: Raisons de santé ou du fait d'un handicap.
+Logement trop cher.
+Logement trop petit.
+Logement trop grand.
+Problèmes d'environnement ou de voisinage
+Violences familiales.
+Autres: Accédant à la propriété en difficulté ou autre motif indiqué par le demandeur.</t>
+  </si>
+  <si>
+    <t>Plus petit que demandé: le ménage a emménagé dans un logement qui dispose d'une pièce en moins par rapport à la plus petite typologie qu'il recherchait
+Conforme à la demande: la typologie du logement attribué est identique à la plus petite typologie recherchée
+Au moins une pièce en plus que demandé: le logement attribué comporte au moins une pièce en plus que la plus petite typologie qu'il recherchait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adéquation entre la typologie recherchée et celle du logement finalement attribué.
+Seule la plus petite typologie recherchée est enregistrée dans le SNE. </t>
+  </si>
+  <si>
+    <t>Adéquation entre la commune d'attribution par rapport aux différents choix initiaux de localisation des ménages</t>
+  </si>
+  <si>
+    <t>Commune demandée en 1er choix : La commune attribuée correspond exactement à la commune recherchée en premier choix par le demandeur.
+Commune demandée en autre choix :La commune attribuée correspond à une commune recherchée, mais hors premier choix.
+Commune dans l'EPCI souhaité : La commune attribuée est située dans le même EPCI qu’une commune recherchée par le demandeur.
+Autre commune du département : La commune attribuée est située dans le même département qu’une commune recherchée.
+Autre commune de la région : La commune attribuée est située dans la même région, mais dans un autre département que les communes recherchées.
+La règle la plus favorable applicable est remontée</t>
+  </si>
+  <si>
+    <t>Nombre de demandes dont l'année de création de la demande correspond à l’année de référence (millésime) de la demande dans le SNE. Exemple: pour le SNE 2024, toutes les demandes créées en 2024 sont des nouvelles demandes</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont la taille du ménage = 1</t>
+  </si>
+  <si>
+    <t>Nombre de nouvelles demandes / Nombre de demandes</t>
+  </si>
+  <si>
+    <t>Nombre de demandes / Nombre d'attributions</t>
+  </si>
+  <si>
+    <t>Nombre de personnes seules / Nombre de demandes</t>
+  </si>
+  <si>
+    <t>Moyenne d'âge des demandeurs</t>
+  </si>
+  <si>
+    <t>Moyenne du revenu fiscal du foyer pour l'année N-2</t>
+  </si>
+  <si>
+    <t>Nombre de demandeurs qui ne sont actuellement pas des locataires Hlm</t>
+  </si>
+  <si>
+    <t>Moyenne de la taille du foyer</t>
+  </si>
+  <si>
+    <t>Nombre d'attributions en mutations / Nombre d'attributions</t>
+  </si>
+  <si>
+    <t>Nombre de demandes de mutation / Nombre de demandes</t>
+  </si>
+  <si>
+    <t>Moyenne du délai d'attribution (en mois)</t>
+  </si>
+  <si>
+    <t>Moyenne de l'ancienneté de la demande au 31 décembre de l'année selectionnée. Il s'agit donc de l'écart entre le jour de la demande de logement social et le 31 décembre de l'année sélectionnée</t>
+  </si>
+  <si>
+    <t>Répartition des demandeurs et des attributaires selon la tranche de ressource par UC</t>
+  </si>
+  <si>
+    <t>Egal à 0 € 
+Entre 1 € et 500 €
+Entre 501 et 1000 € 
+Entre 1001 € et 1500 € 
+Entre 1501 € et 2000 € 
+Plus de 2000 €</t>
+  </si>
+  <si>
+    <t>Locataire Hlm : Ménage locataire Hlmx
+Locataire Hors Hlm: Ménage locataire du parc privé ou titulaire d'un logement de fonction
+Logé gratuitement: Ménage herbergé chez parents/endants/particulier ou logé à titre gratuit
+Logement précaire: Ménage en camping/caravaning, dans un squat, herbergé/logé dans un hôtel, logé en habitat mobile, occupant sans titre, en sous-location ou hébergé dans un logement à titre temporaire.
+Structure d'hébergement: Ménage hébergé dans un centre départemental de l'enfance et de la famille ou centre maternel ou hébergé dans une structure d'hébergement.
+Sans abri: sans abri ou abri de fortune
+Structure collective: Ménage logé en résidence sociale ou foyer ou pension de famille, en RHVS, ou en résidence étudiant.
+Propriétaire occupant</t>
+  </si>
+  <si>
+    <t>Moins d'un an
+Entre 1 et 2 ans
+Entre 2 et 3 ans
+Entre 3 et 4 ans
+Entre 4 et 5 ans
+Plus de 5 ans</t>
+  </si>
+  <si>
+    <t>Répartition des demandeurs et des attributaires selon l'ancienneté de la demande / le délai d'attribution</t>
+  </si>
+  <si>
+    <t>Répartition des demandeurs et des attributaires selon la plafond de ressource</t>
+  </si>
+  <si>
+    <t>Répartition des demandeurs et des attributaires selon la tranche d'âge</t>
+  </si>
+  <si>
+    <t>Répartition des attributaires selon le motif de radiation</t>
+  </si>
+  <si>
+    <t>Egal à 0 €
+Entre 1 € et le PLAI
+Entre le PLAI et le PLUS
+Entre le PLUS et le PLS
+Supérieur au PLS</t>
+  </si>
+  <si>
+    <t>Moins de 20 ans 
+20-24 ans
+25-29 ans
+30-39 ans 
+40-49 ans 
+50-64 ans 
+65 ans et plus</t>
+  </si>
+  <si>
+    <t>Radiation pour abandon de la demande
+Radiation suite à attribution d'un logement
+Radiation suite à irrecevabilité de la demande
+Radiation suite à impossibilité de contacter le demandeur
+Radiation pour cause de non renouvellement</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -342,6 +622,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -382,7 +668,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -390,6 +676,14 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -724,7 +1018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF32A818-55DC-4C7D-829B-81D7B53E1994}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.46484375" customWidth="1"/>
@@ -753,9 +1047,7 @@
       <c r="G1" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>75</v>
-      </c>
+      <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
@@ -775,6 +1067,27 @@
         <v>61</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>63</v>
       </c>
     </row>
@@ -785,9 +1098,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C998C4-4C13-4862-92D5-F4E9358593F6}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
+    <col min="1" max="1" width="18.796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="73.59765625" customWidth="1"/>
     <col min="4" max="4" width="10.6640625" customWidth="1"/>
@@ -969,7 +1283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
@@ -978,6 +1292,226 @@
       </c>
       <c r="C17" s="2" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="57" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -987,15 +1521,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D63C1C-82A7-4D8E-A65D-B74419366C15}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.53125" customWidth="1"/>
     <col min="3" max="3" width="34.46484375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="41.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>64</v>
       </c>
@@ -1009,7 +1543,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>65</v>
       </c>
@@ -1023,7 +1557,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>65</v>
       </c>
@@ -1035,7 +1569,7 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="42.75" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>65</v>
       </c>
@@ -1049,7 +1583,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="114" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="114" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>65</v>
       </c>
@@ -1063,7 +1597,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="128.25" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>65</v>
       </c>
@@ -1077,7 +1611,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>65</v>
       </c>
@@ -1091,7 +1625,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>65</v>
       </c>
@@ -1105,7 +1639,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>65</v>
       </c>
@@ -1119,7 +1653,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="171" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" ht="171" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
         <v>65</v>
       </c>
@@ -1131,6 +1665,161 @@
       </c>
       <c r="D10" s="2" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="171" x14ac:dyDescent="0.45">
+      <c r="A11" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A12" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="270.75" x14ac:dyDescent="0.45">
+      <c r="A13" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A14" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="356.25" x14ac:dyDescent="0.45">
+      <c r="A16" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A17" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="242.25" x14ac:dyDescent="0.45">
+      <c r="A18" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A19" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="A20" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A21" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -1139,23 +1828,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BB913855BB671A4EB6F43A32F07571C2" ma:contentTypeVersion="9" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="24a6ce692c729403999f303a1f20aa38">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bc21b49f-1c27-42ec-8ac6-7a0570c1c596" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cf51073de8832d118423da597a6652a6" ns2:_="">
-    <xsd:import namespace="bc21b49f-1c27-42ec-8ac6-7a0570c1c596"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052237A89E8CA214B92381756AEA23611" ma:contentTypeVersion="19" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="fd32d5d08a6fe5eaace81fdc8054cafd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="44042f46-c638-40f0-b803-0a3c16db3a5d" xmlns:ns3="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="adce47e2ee812e8b8300601e2ac8f257" ns2:_="" ns3:_="">
+    <xsd:import namespace="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
+    <xsd:import namespace="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
+                <xsd:element ref="ns2:Th_x00e8_me" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:Sous_x002d_th_x00e8_me" minOccurs="0"/>
+                <xsd:element ref="ns2:Donn_x00e9_esmobilis_x00e9_es" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:Ann_x00e9_e" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1163,52 +1860,166 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="bc21b49f-1c27-42ec-8ac6-7a0570c1c596" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="44042f46-c638-40f0-b803-0a3c16db3a5d" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+    <xsd:element name="Th_x00e8_me" ma:index="8" nillable="true" ma:displayName="Thème" ma:format="Dropdown" ma:indexed="true" ma:internalName="Th_x00e8_me">
+      <xsd:simpleType>
+        <xsd:union memberTypes="dms:Text">
+          <xsd:simpleType>
+            <xsd:restriction base="dms:Choice">
+              <xsd:enumeration value="Parc"/>
+              <xsd:enumeration value="Accession"/>
+              <xsd:enumeration value="Ménages"/>
+              <xsd:enumeration value="Quittancement"/>
+              <xsd:enumeration value="Références"/>
+              <xsd:enumeration value="Europe"/>
+            </xsd:restriction>
+          </xsd:simpleType>
+        </xsd:union>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="12" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="fd32a620-ee61-41a4-a063-7041d9fb167d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+    <xsd:element name="Sous_x002d_th_x00e8_me" ma:index="13" nillable="true" ma:displayName="Sous-thème" ma:format="Dropdown" ma:internalName="Sous_x002d_th_x00e8_me">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="Programmation"/>
+          <xsd:enumeration value="Agréments"/>
+          <xsd:enumeration value="FNAP"/>
+          <xsd:enumeration value="Financement"/>
+          <xsd:enumeration value="Construction"/>
+          <xsd:enumeration value="Parc social"/>
+          <xsd:enumeration value="Logement adapté"/>
+          <xsd:enumeration value="Logement étudiant"/>
+          <xsd:enumeration value="Foyer"/>
+          <xsd:enumeration value="Résidences spécifiques"/>
+          <xsd:enumeration value="Parc privé"/>
+          <xsd:enumeration value="Réhabilitation"/>
+          <xsd:enumeration value="ANRU"/>
+          <xsd:enumeration value="QPV"/>
+          <xsd:enumeration value="Seconde vie"/>
+          <xsd:enumeration value="DPE"/>
+          <xsd:enumeration value="LLI"/>
+          <xsd:enumeration value="LLS demande"/>
+          <xsd:enumeration value="DALO"/>
+          <xsd:enumeration value="Q1 LEC"/>
+          <xsd:enumeration value="LLS Attribution"/>
+          <xsd:enumeration value="Occupation"/>
+          <xsd:enumeration value="Loyer"/>
+          <xsd:enumeration value="Charge"/>
+          <xsd:enumeration value="APL"/>
+          <xsd:enumeration value="APL Accession"/>
+          <xsd:enumeration value="PTZ"/>
+          <xsd:enumeration value="SLS"/>
+          <xsd:enumeration value="RLS"/>
+          <xsd:enumeration value="RUA"/>
+          <xsd:enumeration value="Impayés"/>
+          <xsd:enumeration value="Incivilités"/>
+          <xsd:enumeration value="Vente Hlm"/>
+          <xsd:enumeration value="Besoin en logement"/>
+          <xsd:enumeration value="PSP"/>
+          <xsd:enumeration value="Surcompensation"/>
+          <xsd:enumeration value="Mutualisation"/>
+          <xsd:enumeration value="Livret A"/>
+          <xsd:enumeration value="Compte consolidé Hlm"/>
+          <xsd:enumeration value="IRL"/>
+          <xsd:enumeration value="Indices et taux"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Donn_x00e9_esmobilis_x00e9_es" ma:index="14" nillable="true" ma:displayName="Données mobilisées" ma:format="Dropdown" ma:internalName="Donn_x00e9_esmobilis_x00e9_es">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="SNE"/>
+          <xsd:enumeration value="OPS"/>
+          <xsd:enumeration value="RPLS"/>
+          <xsd:enumeration value="ENL"/>
+          <xsd:enumeration value="Recensement de la population"/>
+          <xsd:enumeration value="SIAP"/>
+          <xsd:enumeration value="ESH"/>
+          <xsd:enumeration value="OPH"/>
+          <xsd:enumeration value="Indices"/>
+          <xsd:enumeration value="IRL"/>
+          <xsd:enumeration value="Livret A"/>
+          <xsd:enumeration value="OPL"/>
+          <xsd:enumeration value="OVHlm"/>
+          <xsd:enumeration value="Compte du Logement"/>
+          <xsd:enumeration value="Filocom"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="15" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="Ann_x00e9_e" ma:index="19" nillable="true" ma:displayName="Année" ma:decimals="0" ma:format="Dropdown" ma:internalName="Ann_x00e9_e" ma:percentage="FALSE">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Number"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Balises d’images" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="fd32a620-ee61-41a4-a063-7041d9fb167d" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
         </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="23" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{cef1756d-df9b-40a3-be34-4098d20d571d}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="a63d3f7d-9ae7-4881-a2e5-01650a8247b9">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1322,15 +2133,20 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="bc21b49f-1c27-42ec-8ac6-7a0570c1c596">
+    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29D39565-0D10-4DB9-BB30-335C27437E2B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{069710DA-8298-478B-B226-6CE1AAF048CA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1348,7 +2164,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
     <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
-    <ds:schemaRef ds:uri="bc21b49f-1c27-42ec-8ac6-7a0570c1c596"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Documentation dashboards.xlsx
+++ b/Documentation dashboards.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/02 - Données/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/10 - Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="217" documentId="8_{E38240D2-6D03-460C-AD1F-56A7CB9B1EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{492BDCE6-1795-4836-BDB7-7DBFD40DC648}"/>
+  <xr:revisionPtr revIDLastSave="222" documentId="8_{E38240D2-6D03-460C-AD1F-56A7CB9B1EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6D89D36-9B57-4D1E-B2E1-4DE8111D289D}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="1" activeTab="1" xr2:uid="{78D94C61-402A-46A6-8F9B-6154C169E404}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="2" xr2:uid="{78D94C61-402A-46A6-8F9B-6154C169E404}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="3" r:id="rId1"/>
@@ -263,9 +263,6 @@
     <t>Annuel</t>
   </si>
   <si>
-    <t>Direction des etudes</t>
-  </si>
-  <si>
     <t>Dernière date de rafraichissement</t>
   </si>
   <si>
@@ -285,15 +282,6 @@
   </si>
   <si>
     <t>Parc social</t>
-  </si>
-  <si>
-    <t>Portrait du parc social à partir des données du Répertoire du Parc Locatif des bailleurs Sociaux (RPLS) au 1er janvier &lt;annee source rpls&gt;.
-L’objectif est de présenter, pour chaque territoire, une synthèse de l’évolution récente du parc, sa
-répartition selon des catégories habituellement utilisées (type de financement, origine, nombre de
-pièces, localisation en QPV...) ainsi qu’un comparatif des indicateurs clés (rotation, vacance,
-surface et loyer…) par catégorie.
-Seuls les logements locatifs ordinaires sont recensés, les logements foyers ne sont
-donc pas compris dans les résultats. Par ailleurs, les informations présentées portent sur le parc locatif social, au sens strict, et n’intègrent donc pas les logements nonconventionnés des SEM de France métropolitaine</t>
   </si>
   <si>
     <t>Description du theme</t>
@@ -605,12 +593,24 @@
 Radiation suite à impossibilité de contacter le demandeur
 Radiation pour cause de non renouvellement</t>
   </si>
+  <si>
+    <t>Portrait du parc social à partir des données du Répertoire du Parc Locatif des bailleurs Sociaux (RPLS) au 1er janvier
+L’objectif est de présenter, pour chaque territoire, une synthèse de l’évolution récente du parc, sa
+répartition selon des catégories habituellement utilisées (type de financement, origine, nombre de
+pièces, localisation en QPV...) ainsi qu’un comparatif des indicateurs clés (rotation, vacance,
+surface et loyer…) par catégorie.
+Seuls les logements locatifs ordinaires sont recensés, les logements foyers ne sont
+donc pas compris dans les résultats. Par ailleurs, les informations présentées portent sur le parc locatif social, au sens strict, et n’intègrent donc pas les logements nonconventionnés des SEM de France métropolitaine</t>
+  </si>
+  <si>
+    <t>support.data@union-habitat.org</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -628,6 +628,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -665,10 +673,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -680,12 +689,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1027,10 +1034,10 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>55</v>
@@ -1039,59 +1046,63 @@
         <v>56</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="G1" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>58</v>
+        <v>148</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>58</v>
+        <v>74</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>149</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{EAB25B75-F1A1-4ADD-A90A-A502A052CA55}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{4C3DA737-6F2E-421C-84D3-2B4B25E9F2D7}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1109,18 +1120,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -1131,7 +1142,7 @@
     </row>
     <row r="3" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
@@ -1142,7 +1153,7 @@
     </row>
     <row r="4" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>4</v>
@@ -1153,7 +1164,7 @@
     </row>
     <row r="5" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
@@ -1164,18 +1175,18 @@
     </row>
     <row r="6" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>9</v>
@@ -1186,7 +1197,7 @@
     </row>
     <row r="8" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>11</v>
@@ -1197,7 +1208,7 @@
     </row>
     <row r="9" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>13</v>
@@ -1208,7 +1219,7 @@
     </row>
     <row r="10" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>15</v>
@@ -1219,7 +1230,7 @@
     </row>
     <row r="11" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>17</v>
@@ -1230,7 +1241,7 @@
     </row>
     <row r="12" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>19</v>
@@ -1241,7 +1252,7 @@
     </row>
     <row r="13" spans="1:3" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>21</v>
@@ -1252,7 +1263,7 @@
     </row>
     <row r="14" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>23</v>
@@ -1263,7 +1274,7 @@
     </row>
     <row r="15" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>25</v>
@@ -1274,7 +1285,7 @@
     </row>
     <row r="16" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>27</v>
@@ -1285,233 +1296,233 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>108</v>
+        <v>76</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>109</v>
+        <v>78</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1531,21 +1542,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>29</v>
@@ -1559,7 +1570,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>30</v>
@@ -1571,7 +1582,7 @@
     </row>
     <row r="4" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>31</v>
@@ -1585,7 +1596,7 @@
     </row>
     <row r="5" spans="1:5" ht="114" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>32</v>
@@ -1599,7 +1610,7 @@
     </row>
     <row r="6" spans="1:5" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>33</v>
@@ -1613,7 +1624,7 @@
     </row>
     <row r="7" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>34</v>
@@ -1627,7 +1638,7 @@
     </row>
     <row r="8" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>35</v>
@@ -1641,7 +1652,7 @@
     </row>
     <row r="9" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>36</v>
@@ -1655,7 +1666,7 @@
     </row>
     <row r="10" spans="1:5" ht="171" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>37</v>
@@ -1668,158 +1679,158 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="171" x14ac:dyDescent="0.45">
-      <c r="A11" s="8" t="s">
-        <v>75</v>
+      <c r="A11" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="270.75" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A12" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12" s="8" t="s">
+      <c r="C13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="270.75" x14ac:dyDescent="0.45">
-      <c r="A13" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>141</v>
-      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A14" s="8" t="s">
-        <v>75</v>
+      <c r="A14" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:5" ht="142.5" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="356.25" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:5" ht="142.5" x14ac:dyDescent="0.45">
-      <c r="A15" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="1" t="s">
+    </row>
+    <row r="17" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C17" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="242.25" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="356.25" x14ac:dyDescent="0.45">
-      <c r="A16" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A17" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="1" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C19" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="242.25" x14ac:dyDescent="0.45">
-      <c r="A18" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
-      <c r="A19" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" s="1" t="s">
+      <c r="D20" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C21" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
-      <c r="A20" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
-      <c r="A21" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -2146,7 +2157,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{069710DA-8298-478B-B226-6CE1AAF048CA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{069710DA-8298-478B-B226-6CE1AAF048CA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
+    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Documentation dashboards.xlsx
+++ b/Documentation dashboards.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unionhabitat.sharepoint.com/sites/Directiondesetudes/Documents partages/General/Direction/Projets/SI DATA/01 - Projet datawarehouse/10 - Documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="222" documentId="8_{E38240D2-6D03-460C-AD1F-56A7CB9B1EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6D89D36-9B57-4D1E-B2E1-4DE8111D289D}"/>
+  <xr:revisionPtr revIDLastSave="270" documentId="8_{E38240D2-6D03-460C-AD1F-56A7CB9B1EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92565F34-EE0C-4D23-9F15-D94300D44B3F}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" activeTab="2" xr2:uid="{78D94C61-402A-46A6-8F9B-6154C169E404}"/>
+    <workbookView xWindow="38280" yWindow="3795" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{78D94C61-402A-46A6-8F9B-6154C169E404}"/>
   </bookViews>
   <sheets>
     <sheet name="Description" sheetId="3" r:id="rId1"/>
     <sheet name="Indicateurs" sheetId="1" r:id="rId2"/>
     <sheet name="Axes d'analyses" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,68 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="159">
+  <si>
+    <t>Theme</t>
+  </si>
+  <si>
+    <t>Description du theme</t>
+  </si>
+  <si>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>Fréquence de rafraichissement</t>
+  </si>
+  <si>
+    <t>Dernière date de rafraichissement</t>
+  </si>
+  <si>
+    <t>Sources</t>
+  </si>
+  <si>
+    <t>Périmètre géographique</t>
+  </si>
+  <si>
+    <t>Parc social</t>
+  </si>
+  <si>
+    <t>Portrait du parc social à partir des données du Répertoire du Parc Locatif des bailleurs Sociaux (RPLS) au 1er janvier
+L’objectif est de présenter, pour chaque territoire, une synthèse de l’évolution récente du parc, sa
+répartition selon des catégories habituellement utilisées (type de financement, origine, nombre de
+pièces, localisation en QPV...) ainsi qu’un comparatif des indicateurs clés (rotation, vacance,
+surface et loyer…) par catégorie.
+Seuls les logements locatifs ordinaires sont recensés, les logements foyers ne sont
+donc pas compris dans les résultats. Par ailleurs, les informations présentées portent sur le parc locatif social, au sens strict, et n’intègrent donc pas les logements nonconventionnés des SEM de France métropolitaine</t>
+  </si>
+  <si>
+    <t>support.data@union-habitat.org</t>
+  </si>
+  <si>
+    <t>Annuel</t>
+  </si>
+  <si>
+    <t>RPLS, INSEE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toutes les régions de France y compris les  régions d’Outre-Mer </t>
+  </si>
+  <si>
+    <t>Demande et attribution</t>
+  </si>
+  <si>
+    <t>Le rapport sur les demandes et les attributions de logements sociaux est réalisé à partir des données du Système National d’Enregistrement (SNE). Il met en parallèle le profil des demandeurs avec celui des attributaires de logements sociaux et montre l’adéquation entre les attributions et la demande au travers de différents indicateurs. 
+Sont considérés comme « demandeurs » les demandeurs en attente d’un logement social à fin décembre &lt;annee&gt; et sont comptés comme « attributaires » les ménages ayant emménagé dans un logement social durant l’année &lt;annee&gt;. Les chiffres et indicateurs présentés sur le tableau de bord ne prennent pas en compte la demande des associations, mais uniquement celle des demandeurs physiques</t>
+  </si>
+  <si>
+    <t>SNE, INSEE</t>
+  </si>
+  <si>
+    <t>Indicateur</t>
+  </si>
+  <si>
+    <t>Définition</t>
+  </si>
   <si>
     <t xml:space="preserve">Nombre de logements sociaux du parc  </t>
   </si>
@@ -68,6 +129,11 @@
   </si>
   <si>
     <t>Taux de rotation en entrée</t>
+  </si>
+  <si>
+    <t>Taux de logements emmenagés sur l'année
+Si le rpls est sur l'année N alors le taux de rotation est sur l'année N-1
+Calcul: Nombre de logements avec année (BAIL) = N-1 et année(LOCAT) &lt; N-1 / Nombre de logements avec année(LOCAT) &lt; N-1 et proposés à la location mais vacants OU loué avec contrat de location</t>
   </si>
   <si>
     <t>Taux de rotation en sortie</t>
@@ -141,31 +207,141 @@
 Les régions d'outre-mer sont exclus du calcul puisque le DPE GES n'est pas renseigné</t>
   </si>
   <si>
+    <t>Calcul: Nombre de logements sociaux occupés / Nombre de résidences principales privées</t>
+  </si>
+  <si>
+    <t>Nombre de demandes/demandeurs</t>
+  </si>
+  <si>
+    <t>Nombre de ménages demandeurs en attente d'un logement social à fin décembre</t>
+  </si>
+  <si>
+    <t>Nombre de nouvelles demandes</t>
+  </si>
+  <si>
+    <t>Nombre de demandes dont l'année de création de la demande correspond à l’année de référence (millésime) de la demande dans le SNE. Exemple: pour le SNE 2024, toutes les demandes créées en 2024 sont des nouvelles demandes</t>
+  </si>
+  <si>
+    <t>Nombre de demandes en mutation</t>
+  </si>
+  <si>
+    <t>Nombre de ménages demandeurs, actuellement locataires Hlm, en attente d'un logement social à fin décembre de l'année sélectionnée</t>
+  </si>
+  <si>
+    <t>Nombre de personnes seules</t>
+  </si>
+  <si>
+    <t>Nombre de ménages dont la taille du ménage = 1</t>
+  </si>
+  <si>
+    <t>Nombre  de jeunes ménages</t>
+  </si>
+  <si>
+    <t>La dénomination "jeune ménage" recouvre ces catégories de ménage: 
+- les jeunes isolés de moins de 28 ans avec ou sans enfant(s)
+- les jeunes couples avec ou sans enfant(s)
+Jeune couple = couple marié (ou concubins cosignataires du bail) dont la somme des âges est au plus égale à 55 ans.</t>
+  </si>
+  <si>
+    <t>Part des nouvelles demandes</t>
+  </si>
+  <si>
+    <t>Nombre de nouvelles demandes / Nombre de demandes</t>
+  </si>
+  <si>
+    <t>Part des demandes en mutation</t>
+  </si>
+  <si>
+    <t>Nombre de demandes de mutation / Nombre de demandes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ressources / mois / UC </t>
+  </si>
+  <si>
+    <t>Ressources par unité de consommation
+Calcul: Ressources mensuelles du foyer / Nombre d'unités de consommation
+Les ressources comprennent l'ensemble des revenus: revenus du travail, pension de retraite, chômage, prestations sociales…</t>
+  </si>
+  <si>
+    <t>Ancienneté de la demande</t>
+  </si>
+  <si>
+    <t>Moyenne de l'ancienneté de la demande au 31 décembre de l'année selectionnée. Il s'agit donc de l'écart entre le jour de la demande de logement social et le 31 décembre de l'année sélectionnée</t>
+  </si>
+  <si>
+    <t>Pression de la demande</t>
+  </si>
+  <si>
+    <t>Nombre de demandes / Nombre d'attributions</t>
+  </si>
+  <si>
+    <t>Part des personnes seules</t>
+  </si>
+  <si>
+    <t>Nombre de personnes seules / Nombre de demandes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age moyen  </t>
+  </si>
+  <si>
+    <t>Moyenne d'âge des demandeurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenus N-2  </t>
+  </si>
+  <si>
+    <t>Moyenne du revenu fiscal du foyer pour l'année N-2</t>
+  </si>
+  <si>
+    <t>Nombre de primo-demandeurs</t>
+  </si>
+  <si>
+    <t>Nombre de demandeurs qui ne sont actuellement pas des locataires Hlm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taille de ménage  </t>
+  </si>
+  <si>
+    <t>Moyenne de la taille du foyer</t>
+  </si>
+  <si>
+    <t>Nombre d'attributions/attributaires</t>
+  </si>
+  <si>
+    <t>Nombre d'attributions de logements sociaux réalisées durant l'année séléctionnée</t>
+  </si>
+  <si>
+    <t>Nombre d'attributions en mutation</t>
+  </si>
+  <si>
+    <t>Nombre d'attributions réalisées durant l'année sélectionnée pour des ménages changeant de logement au sein du parc Hlm</t>
+  </si>
+  <si>
+    <t>Part des attributions en mutation</t>
+  </si>
+  <si>
+    <t>Nombre d'attributions en mutations / Nombre d'attributions</t>
+  </si>
+  <si>
+    <t>Délai d'attribution</t>
+  </si>
+  <si>
+    <t>Moyenne du délai d'attribution (en mois)</t>
+  </si>
+  <si>
+    <t>Taux de succès</t>
+  </si>
+  <si>
+    <t>Rapport entre le nombre de logements attribués sur l'année sélectionnée et le nombre de demande en stock à fin de l'année sélectionnée</t>
+  </si>
+  <si>
+    <t>Axe</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
     <t>Patrimoine de sortie</t>
-  </si>
-  <si>
-    <t>Période de construction</t>
-  </si>
-  <si>
-    <t>Habitat</t>
-  </si>
-  <si>
-    <t>Type de financement</t>
-  </si>
-  <si>
-    <t>Nombre de pièces</t>
-  </si>
-  <si>
-    <t>Type d'acquisition</t>
-  </si>
-  <si>
-    <t>Etiquette energie</t>
-  </si>
-  <si>
-    <t>Etiquette GES</t>
-  </si>
-  <si>
-    <t>Modalité d'accès PMR</t>
   </si>
   <si>
     <t>Motif de la sortie de patrimoine de l'organisme au cours de l'année civile précédant la collecte</t>
@@ -179,12 +355,24 @@
 9 : Sans objet</t>
   </si>
   <si>
+    <t>Période de construction</t>
+  </si>
+  <si>
+    <t>Ancienneté du logement en année depuis la date de construction</t>
+  </si>
+  <si>
+    <t>Habitat</t>
+  </si>
+  <si>
     <t>Type de construction</t>
   </si>
   <si>
     <t>I : Individuel
 C : Collectif
 E : Etudiant</t>
+  </si>
+  <si>
+    <t>Type de financement</t>
   </si>
   <si>
     <t>Groupe de financement de l'organisme</t>
@@ -200,11 +388,44 @@
 non_soc_inter_reunion: Loyers libres La Réunion</t>
   </si>
   <si>
+    <t>Nombre de pièces</t>
+  </si>
+  <si>
     <t>Nombre de pièces principales du logement</t>
   </si>
   <si>
     <t>Cette notion recouvre les pièces à usage d'habitation (y compris la cuisine si sa surface excède 12 m²) ainsi que les pièces annexes non cédées à des tiers (chambres de service). Ne sont pas comptées les pièces à usage exclusivement professionnel ainsi que les entrées, couloirs, salles de bain, penderies, alcôves, W.-C., buanderies, offices.
 T1 ... T5+</t>
+  </si>
+  <si>
+    <t>Type d'acquisition</t>
+  </si>
+  <si>
+    <t>Mode d'entrée du logement dans le patrimoine du bailleur</t>
+  </si>
+  <si>
+    <t>1 : Construction par l'organisme
+2 : Acquisition avec travaux
+3 : Acquisition sans travaux
+4 : Acquisition en Vefa</t>
+  </si>
+  <si>
+    <t>Etiquette energie</t>
+  </si>
+  <si>
+    <t>Classe de consommation d'énergie</t>
+  </si>
+  <si>
+    <t>A : Consommation d'énergie A
+B : Consommation d'énergie B
+C : Consommation d'énergie C
+D : Consommation d'énergie D
+E : Consommation d'énergie E
+F : Consommation d'énergie F
+G : Consommation d'énergie G</t>
+  </si>
+  <si>
+    <t>Etiquette GES</t>
   </si>
   <si>
     <t>Classe de consommation d'énergie sur l'effet de serre</t>
@@ -219,16 +440,7 @@
 G : Impact sur l'effet de serre G</t>
   </si>
   <si>
-    <t>A : Consommation d'énergie A
-B : Consommation d'énergie B
-C : Consommation d'énergie C
-D : Consommation d'énergie D
-E : Consommation d'énergie E
-F : Consommation d'énergie F
-G : Consommation d'énergie G</t>
-  </si>
-  <si>
-    <t>Classe de consommation d'énergie</t>
+    <t>Modalité d'accès PMR</t>
   </si>
   <si>
     <t>Accessibilité et adaptation du logement aux personnes à mobilité réduite</t>
@@ -242,194 +454,10 @@
 99 : Aucune donnée disponible</t>
   </si>
   <si>
-    <t>Mode d'entrée du logement dans le patrimoine du bailleur</t>
-  </si>
-  <si>
-    <t>1 : Construction par l'organisme
-2 : Acquisition avec travaux
-3 : Acquisition sans travaux
-4 : Acquisition en Vefa</t>
-  </si>
-  <si>
-    <t>Ancienneté du logement en année depuis la date de construction</t>
-  </si>
-  <si>
-    <t>Contact</t>
-  </si>
-  <si>
-    <t>Fréquence de rafraichissement</t>
-  </si>
-  <si>
-    <t>Annuel</t>
-  </si>
-  <si>
-    <t>Dernière date de rafraichissement</t>
-  </si>
-  <si>
-    <t>Sources</t>
-  </si>
-  <si>
-    <t>RPLS, INSEE</t>
-  </si>
-  <si>
-    <t>Périmètre géographique</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toutes les régions de France y compris les  régions d’Outre-Mer </t>
-  </si>
-  <si>
-    <t>Theme</t>
-  </si>
-  <si>
-    <t>Parc social</t>
-  </si>
-  <si>
-    <t>Description du theme</t>
-  </si>
-  <si>
-    <t>Indicateur</t>
-  </si>
-  <si>
-    <t>Définition</t>
-  </si>
-  <si>
-    <t>Axe</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Taux de logements emmenagés sur l'année
-Si le rpls est sur l'année N alors le taux de rotation est sur l'année N-1
-Calcul: Nombre de logements avec année (BAIL) = N-1 et année(LOCAT) &lt; N-1 / Nombre de logements avec année(LOCAT) &lt; N-1 et proposés à la location mais vacants OU loué avec contrat de location</t>
-  </si>
-  <si>
-    <t>Taux de locataires sociaux</t>
-  </si>
-  <si>
-    <t>Calcul: Nombre de logements sociaux occupés / Nombre de résidences principales privées</t>
-  </si>
-  <si>
-    <t>Demande et attribution</t>
-  </si>
-  <si>
-    <t>Le rapport sur les demandes et les attributions de logements sociaux est réalisé à partir des données du Système National d’Enregistrement (SNE). Il met en parallèle le profil des demandeurs avec celui des attributaires de logements sociaux et montre l’adéquation entre les attributions et la demande au travers de différents indicateurs. 
-Sont considérés comme « demandeurs » les demandeurs en attente d’un logement social à fin décembre &lt;annee&gt; et sont comptés comme « attributaires » les ménages ayant emménagé dans un logement social durant l’année &lt;annee&gt;. Les chiffres et indicateurs présentés sur le tableau de bord ne prennent pas en compte la demande des associations, mais uniquement celle des demandeurs physiques</t>
-  </si>
-  <si>
-    <t>SNE, INSEE</t>
-  </si>
-  <si>
-    <t>Nombre de demandes/demandeurs</t>
-  </si>
-  <si>
-    <t>Nombre de nouvelles demandes</t>
-  </si>
-  <si>
-    <t>Nombre de demandes en mutation</t>
-  </si>
-  <si>
-    <t>Part des nouvelles demandes</t>
-  </si>
-  <si>
-    <t>Part des demandes en mutation</t>
-  </si>
-  <si>
-    <t>Ancienneté de la demande</t>
-  </si>
-  <si>
-    <t>Pression de la demande</t>
-  </si>
-  <si>
-    <t>Nombre de primo-demandeurs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ressources / mois / UC </t>
-  </si>
-  <si>
-    <t>Nombre d'attributions/attributaires</t>
-  </si>
-  <si>
-    <t>Nombre d'attributions en mutation</t>
-  </si>
-  <si>
-    <t>Part des attributions en mutation</t>
-  </si>
-  <si>
-    <t>Délai d'attribution</t>
-  </si>
-  <si>
-    <t>Taux de succès</t>
-  </si>
-  <si>
-    <t>Nombre de personnes seules</t>
-  </si>
-  <si>
-    <t>Nombre  de jeunes ménages</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taille de ménage  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age moyen  </t>
-  </si>
-  <si>
-    <t>Part des personnes seules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revenus N-2  </t>
-  </si>
-  <si>
     <t>Composition familiale</t>
   </si>
   <si>
-    <t>Tranche de ressources par UC</t>
-  </si>
-  <si>
-    <t>Mode de logement</t>
-  </si>
-  <si>
-    <t>Nombre de pièces adéquation</t>
-  </si>
-  <si>
-    <t>Motif de la demande</t>
-  </si>
-  <si>
-    <t>Tranche d'ancienneté demande / délai d'attribution</t>
-  </si>
-  <si>
-    <t>Localisation</t>
-  </si>
-  <si>
-    <t>Tranche de plafonds de ressources</t>
-  </si>
-  <si>
-    <t>Tranche d'âge</t>
-  </si>
-  <si>
-    <t>Motif de radiation</t>
-  </si>
-  <si>
-    <t>Nombre de ménages demandeurs en attente d'un logement social à fin décembre</t>
-  </si>
-  <si>
-    <t>Nombre de ménages demandeurs, actuellement locataires Hlm, en attente d'un logement social à fin décembre de l'année sélectionnée</t>
-  </si>
-  <si>
-    <t>Nombre d'attributions de logements sociaux réalisées durant l'année séléctionnée</t>
-  </si>
-  <si>
-    <t>Nombre d'attributions réalisées durant l'année sélectionnée pour des ménages changeant de logement au sein du parc Hlm</t>
-  </si>
-  <si>
-    <t>Rapport entre le nombre de logements attribués sur l'année sélectionnée et le nombre de demande en stock à fin de l'année sélectionnée</t>
-  </si>
-  <si>
     <t>Répartition des demandeurs et des attributaires selon la composition familiale du ménage</t>
-  </si>
-  <si>
-    <t>verifier pour le co titulaire couple
-verifier famille mono</t>
   </si>
   <si>
     <t>Isolé: Ménage formé d'une seule personne
@@ -438,21 +466,56 @@
 Autre: Ménages n'entrant pas dans les catégories sus-citées.</t>
   </si>
   <si>
-    <t>La dénomination "jeune ménage" recouvre ces catégories de ménage: 
-- les jeunes isolés de moins de 28 ans avec ou sans enfant(s)
-- les jeunes couples avec ou sans enfant(s)
-Jeune couple = couple marié (ou concubins cosignataires du bail) dont la somme des âges est au plus égale à 55 ans.</t>
-  </si>
-  <si>
-    <t>Ressources par unité de consommation
-Calcul: Ressources mensuelles du foyer / Nombre d'unités de consommation
-Les ressources comprennent l'ensemble des revenus: revenus du travail, pension de retraite, chômage, prestations sociales…</t>
+    <t>verifier pour le co titulaire couple
+verifier famille mono</t>
+  </si>
+  <si>
+    <t>Tranche de ressources par UC</t>
+  </si>
+  <si>
+    <t>Répartition des demandeurs et des attributaires selon la tranche de ressource par UC</t>
+  </si>
+  <si>
+    <t>Egal à 0 € 
+Entre 1 € et 500 €
+Entre 501 et 1000 € 
+Entre 1001 € et 1500 € 
+Entre 1501 € et 2000 € 
+Plus de 2000 €</t>
+  </si>
+  <si>
+    <t>Mode de logement</t>
   </si>
   <si>
     <t>Répartition des demandeurs et des attributaires selon leur mode de logement antérieur</t>
   </si>
   <si>
+    <t>Locataire Hlm : Ménage locataire Hlmx
+Locataire Hors Hlm: Ménage locataire du parc privé ou titulaire d'un logement de fonction
+Logé gratuitement: Ménage herbergé chez parents/endants/particulier ou logé à titre gratuit
+Logement précaire: Ménage en camping/caravaning, dans un squat, herbergé/logé dans un hôtel, logé en habitat mobile, occupant sans titre, en sous-location ou hébergé dans un logement à titre temporaire.
+Structure d'hébergement: Ménage hébergé dans un centre départemental de l'enfance et de la famille ou centre maternel ou hébergé dans une structure d'hébergement.
+Sans abri: sans abri ou abri de fortune
+Structure collective: Ménage logé en résidence sociale ou foyer ou pension de famille, en RHVS, ou en résidence étudiant.
+Propriétaire occupant</t>
+  </si>
+  <si>
     <t>Répartition des demandeurs selon le type de logement recherché et celle des attributaires selon la typologie du logement attribué</t>
+  </si>
+  <si>
+    <t>Nombre de pièces adéquation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adéquation entre la typologie recherchée et celle du logement finalement attribué.
+Seule la plus petite typologie recherchée est enregistrée dans le SNE. </t>
+  </si>
+  <si>
+    <t>Plus petit que demandé: le ménage a emménagé dans un logement qui dispose d'une pièce en moins par rapport à la plus petite typologie qu'il recherchait
+Conforme à la demande: la typologie du logement attribué est identique à la plus petite typologie recherchée
+Au moins une pièce en plus que demandé: le logement attribué comporte au moins une pièce en plus que la plus petite typologie qu'il recherchait</t>
+  </si>
+  <si>
+    <t>Motif de la demande</t>
   </si>
   <si>
     <t xml:space="preserve">Motifs évoqués par les demandeurs </t>
@@ -471,13 +534,21 @@
 Autres: Accédant à la propriété en difficulté ou autre motif indiqué par le demandeur.</t>
   </si>
   <si>
-    <t>Plus petit que demandé: le ménage a emménagé dans un logement qui dispose d'une pièce en moins par rapport à la plus petite typologie qu'il recherchait
-Conforme à la demande: la typologie du logement attribué est identique à la plus petite typologie recherchée
-Au moins une pièce en plus que demandé: le logement attribué comporte au moins une pièce en plus que la plus petite typologie qu'il recherchait</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adéquation entre la typologie recherchée et celle du logement finalement attribué.
-Seule la plus petite typologie recherchée est enregistrée dans le SNE. </t>
+    <t>Tranche d'ancienneté demande / délai d'attribution</t>
+  </si>
+  <si>
+    <t>Répartition des demandeurs et des attributaires selon l'ancienneté de la demande / le délai d'attribution</t>
+  </si>
+  <si>
+    <t>Moins d'un an
+Entre 1 et 2 ans
+Entre 2 et 3 ans
+Entre 3 et 4 ans
+Entre 4 et 5 ans
+Plus de 5 ans</t>
+  </si>
+  <si>
+    <t>Localisation</t>
   </si>
   <si>
     <t>Adéquation entre la commune d'attribution par rapport aux différents choix initiaux de localisation des ménages</t>
@@ -491,84 +562,10 @@
 La règle la plus favorable applicable est remontée</t>
   </si>
   <si>
-    <t>Nombre de demandes dont l'année de création de la demande correspond à l’année de référence (millésime) de la demande dans le SNE. Exemple: pour le SNE 2024, toutes les demandes créées en 2024 sont des nouvelles demandes</t>
-  </si>
-  <si>
-    <t>Nombre de ménages dont la taille du ménage = 1</t>
-  </si>
-  <si>
-    <t>Nombre de nouvelles demandes / Nombre de demandes</t>
-  </si>
-  <si>
-    <t>Nombre de demandes / Nombre d'attributions</t>
-  </si>
-  <si>
-    <t>Nombre de personnes seules / Nombre de demandes</t>
-  </si>
-  <si>
-    <t>Moyenne d'âge des demandeurs</t>
-  </si>
-  <si>
-    <t>Moyenne du revenu fiscal du foyer pour l'année N-2</t>
-  </si>
-  <si>
-    <t>Nombre de demandeurs qui ne sont actuellement pas des locataires Hlm</t>
-  </si>
-  <si>
-    <t>Moyenne de la taille du foyer</t>
-  </si>
-  <si>
-    <t>Nombre d'attributions en mutations / Nombre d'attributions</t>
-  </si>
-  <si>
-    <t>Nombre de demandes de mutation / Nombre de demandes</t>
-  </si>
-  <si>
-    <t>Moyenne du délai d'attribution (en mois)</t>
-  </si>
-  <si>
-    <t>Moyenne de l'ancienneté de la demande au 31 décembre de l'année selectionnée. Il s'agit donc de l'écart entre le jour de la demande de logement social et le 31 décembre de l'année sélectionnée</t>
-  </si>
-  <si>
-    <t>Répartition des demandeurs et des attributaires selon la tranche de ressource par UC</t>
-  </si>
-  <si>
-    <t>Egal à 0 € 
-Entre 1 € et 500 €
-Entre 501 et 1000 € 
-Entre 1001 € et 1500 € 
-Entre 1501 € et 2000 € 
-Plus de 2000 €</t>
-  </si>
-  <si>
-    <t>Locataire Hlm : Ménage locataire Hlmx
-Locataire Hors Hlm: Ménage locataire du parc privé ou titulaire d'un logement de fonction
-Logé gratuitement: Ménage herbergé chez parents/endants/particulier ou logé à titre gratuit
-Logement précaire: Ménage en camping/caravaning, dans un squat, herbergé/logé dans un hôtel, logé en habitat mobile, occupant sans titre, en sous-location ou hébergé dans un logement à titre temporaire.
-Structure d'hébergement: Ménage hébergé dans un centre départemental de l'enfance et de la famille ou centre maternel ou hébergé dans une structure d'hébergement.
-Sans abri: sans abri ou abri de fortune
-Structure collective: Ménage logé en résidence sociale ou foyer ou pension de famille, en RHVS, ou en résidence étudiant.
-Propriétaire occupant</t>
-  </si>
-  <si>
-    <t>Moins d'un an
-Entre 1 et 2 ans
-Entre 2 et 3 ans
-Entre 3 et 4 ans
-Entre 4 et 5 ans
-Plus de 5 ans</t>
-  </si>
-  <si>
-    <t>Répartition des demandeurs et des attributaires selon l'ancienneté de la demande / le délai d'attribution</t>
+    <t>Tranche de plafonds de ressources</t>
   </si>
   <si>
     <t>Répartition des demandeurs et des attributaires selon la plafond de ressource</t>
-  </si>
-  <si>
-    <t>Répartition des demandeurs et des attributaires selon la tranche d'âge</t>
-  </si>
-  <si>
-    <t>Répartition des attributaires selon le motif de radiation</t>
   </si>
   <si>
     <t>Egal à 0 €
@@ -576,6 +573,12 @@
 Entre le PLAI et le PLUS
 Entre le PLUS et le PLS
 Supérieur au PLS</t>
+  </si>
+  <si>
+    <t>Tranche d'âge</t>
+  </si>
+  <si>
+    <t>Répartition des demandeurs et des attributaires selon la tranche d'âge</t>
   </si>
   <si>
     <t>Moins de 20 ans 
@@ -587,6 +590,12 @@
 65 ans et plus</t>
   </si>
   <si>
+    <t>Motif de radiation</t>
+  </si>
+  <si>
+    <t>Répartition des attributaires selon le motif de radiation</t>
+  </si>
+  <si>
     <t>Radiation pour abandon de la demande
 Radiation suite à attribution d'un logement
 Radiation suite à irrecevabilité de la demande
@@ -594,16 +603,46 @@
 Radiation pour cause de non renouvellement</t>
   </si>
   <si>
-    <t>Portrait du parc social à partir des données du Répertoire du Parc Locatif des bailleurs Sociaux (RPLS) au 1er janvier
-L’objectif est de présenter, pour chaque territoire, une synthèse de l’évolution récente du parc, sa
-répartition selon des catégories habituellement utilisées (type de financement, origine, nombre de
-pièces, localisation en QPV...) ainsi qu’un comparatif des indicateurs clés (rotation, vacance,
-surface et loyer…) par catégorie.
-Seuls les logements locatifs ordinaires sont recensés, les logements foyers ne sont
-donc pas compris dans les résultats. Par ailleurs, les informations présentées portent sur le parc locatif social, au sens strict, et n’intègrent donc pas les logements nonconventionnés des SEM de France métropolitaine</t>
-  </si>
-  <si>
-    <t>support.data@union-habitat.org</t>
+    <t>Part de locataires sociaux</t>
+  </si>
+  <si>
+    <t>DALO</t>
+  </si>
+  <si>
+    <t>Premier quartile</t>
+  </si>
+  <si>
+    <t>Logement d'abord</t>
+  </si>
+  <si>
+    <t>Demandeurs et attributaires reconnus prioritaires au titre DALO</t>
+  </si>
+  <si>
+    <t>Demandeurs et attributaires dont les ressources se situent sous le premier quartile de ressources sur les territoires concernés par la réforme des attributions</t>
+  </si>
+  <si>
+    <t>Demandeurs et attributaires bénéficiant du plan Logement d'abord</t>
+  </si>
+  <si>
+    <t>Il s'agit d'une demande ou d'une attribution Logement d'abord ssi, le mode de logement actuel correspond à :
+- Résidence sociale, foyer
+- RHVS
+- Logement temporaire
+- Structure d'hébergement
+- Centre enfance famille
+- Hôtel
+- Sans abri
+- Squat
+- Coordination thérapeutique</t>
+  </si>
+  <si>
+    <t>Il s'agit d'une demande ou d'une attribution Premier quartile ssi (montant du revenu mensuel du foyer / unité de consommation) x 12 mois &lt;= montant du seuil de ressources</t>
+  </si>
+  <si>
+    <t>Il s'agit d'une demande ou d'une attribution DALO ssi :
+- le statut dalo est différent de NON
+- le statut dalo n'est pas null
+- la date de décision dalo &lt;= 31/12/N</t>
   </si>
 </sst>
 </file>
@@ -649,7 +688,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -672,12 +711,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -690,6 +740,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1026,76 +1079,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF32A818-55DC-4C7D-829B-81D7B53E1994}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.46484375" customWidth="1"/>
-    <col min="2" max="2" width="109.06640625" customWidth="1"/>
+    <col min="1" max="1" width="10.3984375" customWidth="1"/>
+    <col min="2" max="2" width="109" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>149</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>149</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1110,419 +1163,419 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C998C4-4C13-4862-92D5-F4E9358593F6}">
   <dimension ref="A1:C37"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.86328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="73.59765625" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>71</v>
+        <v>149</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>124</v>
+        <v>51</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>114</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>126</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="57" x14ac:dyDescent="0.45">
       <c r="A25" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A26" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>127</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A28" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>128</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A29" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>129</v>
+        <v>72</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="C30" s="2" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A31" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>131</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A32" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>132</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>108</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A34" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A35" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A36" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>135</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A37" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1532,306 +1585,364 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08D63C1C-82A7-4D8E-A65D-B74419366C15}">
-  <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="33.53125" customWidth="1"/>
-    <col min="3" max="3" width="34.46484375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.3984375" customWidth="1"/>
+    <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="2" max="2" width="33.59765625" customWidth="1"/>
+    <col min="3" max="3" width="34.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="53.265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>54</v>
+        <v>94</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="D3" s="1"/>
     </row>
     <row r="4" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>40</v>
+        <v>96</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="114" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>42</v>
+        <v>99</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="128.25" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>44</v>
+        <v>102</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>52</v>
+        <v>105</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>49</v>
+        <v>108</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>46</v>
+        <v>111</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="171" x14ac:dyDescent="0.45">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>50</v>
+        <v>114</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>115</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="171" x14ac:dyDescent="0.45">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="187.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>118</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A12" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>137</v>
+        <v>121</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="270.75" x14ac:dyDescent="0.45">
       <c r="A13" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>116</v>
+        <v>124</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>125</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A14" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>117</v>
+        <v>102</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="D14" s="1"/>
     </row>
-    <row r="15" spans="1:5" ht="142.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" ht="171" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="356.25" x14ac:dyDescent="0.45">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="285" x14ac:dyDescent="0.45">
       <c r="A16" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>118</v>
+        <v>131</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A17" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>141</v>
+        <v>134</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="242.25" x14ac:dyDescent="0.45">
       <c r="A18" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>122</v>
+        <v>137</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>138</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A19" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C19" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A20" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="1" t="s">
         <v>143</v>
       </c>
+      <c r="C20" s="2" t="s">
+        <v>144</v>
+      </c>
       <c r="D20" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A21" s="1" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>147</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>147</v>
-      </c>
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="71.25" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="57" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="171" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C25" s="5"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C27" s="5"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C29" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1839,8 +1950,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052237A89E8CA214B92381756AEA23611" ma:contentTypeVersion="19" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="fd32d5d08a6fe5eaace81fdc8054cafd">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="44042f46-c638-40f0-b803-0a3c16db3a5d" xmlns:ns3="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="adce47e2ee812e8b8300601e2ac8f257" ns2:_="" ns3:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010052237A89E8CA214B92381756AEA23611" ma:contentTypeVersion="20" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="510f2d890aca16c7e52118f19c292bce">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="44042f46-c638-40f0-b803-0a3c16db3a5d" xmlns:ns3="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5bb1233f2449b16a4f87373320f89a9" ns2:_="" ns3:_="">
     <xsd:import namespace="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
     <xsd:import namespace="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
     <xsd:element name="properties">
@@ -1864,6 +1990,7 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -2017,6 +2144,11 @@
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="24" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -2132,7 +2264,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -2141,23 +2273,19 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Sous_x002d_th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Ann_x00e9_e xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Donn_x00e9_esmobilis_x00e9_es xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <Th_x00e8_me xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="44042f46-c638-40f0-b803-0a3c16db3a5d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="a63d3f7d-9ae7-4881-a2e5-01650a8247b9" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB5A1737-75AC-4C46-9CF2-0725CB708A15}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
+    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{069710DA-8298-478B-B226-6CE1AAF048CA}">
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C7AC71B-59C7-4E14-BBB6-8E6DAC860991}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -2175,21 +2303,10 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F53CA91-B762-4110-8F3F-3FE1EDA322A6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB5A1737-75AC-4C46-9CF2-0725CB708A15}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="44042f46-c638-40f0-b803-0a3c16db3a5d"/>
-    <ds:schemaRef ds:uri="a63d3f7d-9ae7-4881-a2e5-01650a8247b9"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>